--- a/MainTop/25.04.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/25.04.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\25.04.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A845C64-E536-49A9-BE8C-75AF0379E295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183DE33F-5E87-48F0-A0BE-E2DEC57723BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="88">
   <si>
     <t>Артикул</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Термонаклейка Тигр розовый крупный план</t>
+  </si>
+  <si>
+    <t>на 4 города</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -356,11 +359,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -369,6 +381,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -671,13 +686,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,8 +717,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J1" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -728,8 +746,12 @@
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <f>F2/4</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -754,8 +776,12 @@
       <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="0">F3/4</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -780,8 +806,12 @@
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -806,8 +836,12 @@
       <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -832,8 +866,12 @@
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -858,8 +896,12 @@
       <c r="H7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -884,8 +926,12 @@
       <c r="H8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -910,8 +956,12 @@
       <c r="H9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -936,8 +986,12 @@
       <c r="H10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -962,8 +1016,12 @@
       <c r="H11" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -988,8 +1046,12 @@
       <c r="H12" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -1014,8 +1076,12 @@
       <c r="H13" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1040,8 +1106,12 @@
       <c r="H14" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -1066,8 +1136,12 @@
       <c r="H15" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1092,8 +1166,12 @@
       <c r="H16" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1118,8 +1196,12 @@
       <c r="H17" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1144,8 +1226,12 @@
       <c r="H18" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1170,8 +1256,12 @@
       <c r="H19" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1196,8 +1286,12 @@
       <c r="H20" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -1222,8 +1316,12 @@
       <c r="H21" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -1248,8 +1346,12 @@
       <c r="H22" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1274,8 +1376,12 @@
       <c r="H23" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -1300,8 +1406,12 @@
       <c r="H24" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
@@ -1326,8 +1436,12 @@
       <c r="H25" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
@@ -1352,8 +1466,12 @@
       <c r="H26" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
@@ -1378,8 +1496,12 @@
       <c r="H27" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -1404,8 +1526,12 @@
       <c r="H28" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
@@ -1430,8 +1556,12 @@
       <c r="H29" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -1456,8 +1586,12 @@
       <c r="H30" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
@@ -1482,8 +1616,12 @@
       <c r="H31" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
@@ -1508,8 +1646,12 @@
       <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
@@ -1534,8 +1676,12 @@
       <c r="H33" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
@@ -1560,8 +1706,12 @@
       <c r="H34" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>44</v>
       </c>
@@ -1586,8 +1736,12 @@
       <c r="H35" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -1612,8 +1766,12 @@
       <c r="H36" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -1638,8 +1796,12 @@
       <c r="H37" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>47</v>
       </c>
@@ -1664,8 +1826,12 @@
       <c r="H38" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J38">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>48</v>
       </c>
@@ -1690,8 +1856,12 @@
       <c r="H39" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>49</v>
       </c>
@@ -1716,8 +1886,12 @@
       <c r="H40" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J40">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>50</v>
       </c>
@@ -1742,8 +1916,12 @@
       <c r="H41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>51</v>
       </c>
@@ -1768,8 +1946,12 @@
       <c r="H42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>52</v>
       </c>
@@ -1794,8 +1976,12 @@
       <c r="H43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
@@ -1820,8 +2006,12 @@
       <c r="H44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>54</v>
       </c>
@@ -1846,8 +2036,12 @@
       <c r="H45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>55</v>
       </c>
@@ -1872,8 +2066,12 @@
       <c r="H46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>56</v>
       </c>
@@ -1898,8 +2096,12 @@
       <c r="H47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>57</v>
       </c>
@@ -1924,8 +2126,12 @@
       <c r="H48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>58</v>
       </c>
@@ -1950,8 +2156,12 @@
       <c r="H49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>59</v>
       </c>
@@ -1976,8 +2186,12 @@
       <c r="H50" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>60</v>
       </c>
@@ -2002,8 +2216,12 @@
       <c r="H51" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>61</v>
       </c>
@@ -2028,8 +2246,12 @@
       <c r="H52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>62</v>
       </c>
@@ -2054,8 +2276,12 @@
       <c r="H53" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>63</v>
       </c>
@@ -2080,8 +2306,12 @@
       <c r="H54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J54">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>64</v>
       </c>
@@ -2106,8 +2336,12 @@
       <c r="H55" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J55">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -2132,8 +2366,12 @@
       <c r="H56" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>66</v>
       </c>
@@ -2158,8 +2396,12 @@
       <c r="H57" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>67</v>
       </c>
@@ -2184,8 +2426,12 @@
       <c r="H58" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
@@ -2210,8 +2456,12 @@
       <c r="H59" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J59">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
@@ -2236,8 +2486,12 @@
       <c r="H60" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
@@ -2262,8 +2516,12 @@
       <c r="H61" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J61">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>71</v>
       </c>
@@ -2288,8 +2546,12 @@
       <c r="H62" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J62">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>72</v>
       </c>
@@ -2314,8 +2576,12 @@
       <c r="H63" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J63">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>73</v>
       </c>
@@ -2340,8 +2606,12 @@
       <c r="H64" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>74</v>
       </c>
@@ -2366,8 +2636,12 @@
       <c r="H65" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>75</v>
       </c>
@@ -2392,8 +2666,12 @@
       <c r="H66" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>76</v>
       </c>
@@ -2418,8 +2696,12 @@
       <c r="H67" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J67">
+        <f t="shared" ref="J67:J76" si="1">F67/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>77</v>
       </c>
@@ -2444,8 +2726,12 @@
       <c r="H68" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J68">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>78</v>
       </c>
@@ -2470,8 +2756,12 @@
       <c r="H69" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J69">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>79</v>
       </c>
@@ -2496,8 +2786,12 @@
       <c r="H70" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J70">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>80</v>
       </c>
@@ -2522,8 +2816,12 @@
       <c r="H71" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J71">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>81</v>
       </c>
@@ -2548,8 +2846,12 @@
       <c r="H72" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J72">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>82</v>
       </c>
@@ -2574,8 +2876,12 @@
       <c r="H73" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J73">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>83</v>
       </c>
@@ -2600,8 +2906,12 @@
       <c r="H74" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J74">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>84</v>
       </c>
@@ -2626,8 +2936,12 @@
       <c r="H75" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J75">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>86</v>
       </c>
@@ -2651,6 +2965,16 @@
       </c>
       <c r="H76" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J77">
+        <f>SUM(J2:J76)</f>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
